--- a/tests/gold-project/outputs/schedule/Day Out of Days.xlsx
+++ b/tests/gold-project/outputs/schedule/Day Out of Days.xlsx
@@ -1672,7 +1672,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200"/>
   <headerFooter>
-    <oddFooter>&amp;CCreated with OpenFrame Studio</oddFooter>
+    <oddFooter>&amp;CCreated using OpenFrame</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
